--- a/san_automation_info.xlsx
+++ b/san_automation_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\05.PYTHON\Projects\san_report_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7951195-6BD5-4190-AAE2-4C2BA32C86DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FEF7DE-4A2E-43A5-8114-B8F9D560239F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" firstSheet="8" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" firstSheet="5" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contents" sheetId="1" r:id="rId1"/>
@@ -62,6 +62,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -70,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11786" uniqueCount="5160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11826" uniqueCount="5177">
   <si>
     <t>Contents</t>
   </si>
@@ -16328,6 +16331,57 @@
   </si>
   <si>
     <t>hostid_name_params</t>
+  </si>
+  <si>
+    <t>ALL_F_PORTS(TX/hour&gt;90.00)</t>
+  </si>
+  <si>
+    <t>e8:a6:60</t>
+  </si>
+  <si>
+    <t>c8:84:cf</t>
+  </si>
+  <si>
+    <t>^(\d{4}/\d{2}/\d{2}-\d{2}:\d{2}:\d{2}) *(?:\(\w*\))*, +\[(.+?)], (\d+), (.+?), (\w+), ([\w.-]+), +(.+?). *$</t>
+  </si>
+  <si>
+    <t>2025/01/31-12:01:17 (MSK), [NS-1024], 541678, FID 128, INFO, n3-g620-011-vc5-f1,  Flow from device 0x0b0000 to quarantined device 0x031b00 of Remote domain 3 has been successfully quarantined.</t>
+  </si>
+  <si>
+    <t>2025/01/31-15:27:30 (MSK), [MAPS-1005], 51869, FID 128 | PORT 0/40, WARNING, n1-g620-023-nord152-f1, ISL to san09-nord port 40, E-Port 40, Condition=ALL_PORTS(PORT_BANDWIDTH/NONE==OVERSUBSCRIBED), Current Value:[PORT_BANDWIDTH, OVERSUBSCRIBED], Rule defALL_PORTS_OVERSUBSCRIBED triggered 3 times in 15 min and last trigger time Fri Jan 31 15:14:00 2025, Dashboard Categor                                    y=Fabric Performance Impact.</t>
+  </si>
+  <si>
+    <t>c0:e1:be</t>
+  </si>
+  <si>
+    <t>44:9b:c1</t>
+  </si>
+  <si>
+    <t>e0:da:90</t>
+  </si>
+  <si>
+    <t>98:48:74</t>
+  </si>
+  <si>
+    <t>1c:e6:39</t>
+  </si>
+  <si>
+    <t>flow_from_to_quarantined device</t>
+  </si>
+  <si>
+    <t>^Flow from device 0x(\w+) to quarantined device 0x(\w+).+</t>
+  </si>
+  <si>
+    <t>Flow from device 0x181700 to quarantined device 0x180f00 of Local domain 24 has been successfully quarantined</t>
+  </si>
+  <si>
+    <t>Flow from device 0x181000 to quarantined device 0x180f00 of Local domain 24 has been successfully unquarantined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x181700 0x180f00 </t>
+  </si>
+  <si>
+    <t>flow sid did un(quarantined)</t>
   </si>
 </sst>
 </file>
@@ -16446,7 +16500,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="73">
+  <fills count="74">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -16879,6 +16933,12 @@
         <bgColor rgb="FFD7E4BD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor rgb="FFD7E4BD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -16908,7 +16968,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -17076,12 +17136,23 @@
     <xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="71" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="72" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18037,7 +18108,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
@@ -18045,14 +18116,14 @@
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="39.42578125" customWidth="1"/>
     <col min="5" max="5" width="78.42578125" customWidth="1"/>
-    <col min="6" max="6" width="45.42578125" customWidth="1"/>
+    <col min="6" max="6" width="131.140625" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="16.28515625" customWidth="1"/>
     <col min="9" max="9" width="31" customWidth="1"/>
     <col min="10" max="10" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18084,12 +18155,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>884</v>
       </c>
@@ -18121,12 +18192,12 @@
         <v>893</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I4" s="24" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>1280</v>
       </c>
@@ -18134,12 +18205,12 @@
         <v>910</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I6" s="12" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -18159,7 +18230,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>1285</v>
       </c>
@@ -18167,17 +18238,17 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>1286</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I10" t="s">
         <v>1287</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1</v>
       </c>
@@ -18185,7 +18256,7 @@
         <v>1288</v>
       </c>
       <c r="E11" t="s">
-        <v>1289</v>
+        <v>5163</v>
       </c>
       <c r="F11" t="s">
         <v>1290</v>
@@ -18193,23 +18264,32 @@
       <c r="I11" t="s">
         <v>1291</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>5164</v>
+      </c>
       <c r="I12" t="s">
         <v>1292</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>5165</v>
+      </c>
       <c r="I13" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>1294</v>
       </c>
@@ -18248,7 +18328,7 @@
     <hyperlink ref="J1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0800-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24917,19 +24997,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E155 G154 E157:E160 E162:E163 E165:E167 E169:E1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E156 G156:I156">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E161 G161">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E164 G164">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E168 G168">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
@@ -35987,7 +36067,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:T121"/>
+  <dimension ref="A1:T124"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -35995,7 +36075,7 @@
     <col min="3" max="3" width="22.42578125" customWidth="1"/>
     <col min="4" max="4" width="23.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.42578125" customWidth="1"/>
     <col min="7" max="7" width="125.140625" customWidth="1"/>
     <col min="8" max="8" width="231.42578125" customWidth="1"/>
     <col min="9" max="9" width="105.85546875" customWidth="1"/>
@@ -37385,7 +37465,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B114" s="49" t="s">
         <v>1301</v>
       </c>
@@ -37411,17 +37491,17 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H115" s="49" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H116" s="49" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B118" s="43" t="s">
         <v>1301</v>
       </c>
@@ -37444,12 +37524,12 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H119" s="43" t="s">
         <v>1459</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B121" s="127" t="s">
         <v>1301</v>
       </c>
@@ -37473,6 +37553,43 @@
       </c>
       <c r="I121" s="128" t="s">
         <v>5106</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="131" t="s">
+        <v>5176</v>
+      </c>
+      <c r="B123" s="131" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C123" s="131" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D123" s="131" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E123" s="114">
+        <v>17</v>
+      </c>
+      <c r="F123" s="131" t="s">
+        <v>5171</v>
+      </c>
+      <c r="G123" s="131" t="s">
+        <v>5172</v>
+      </c>
+      <c r="H123" s="131" t="s">
+        <v>5173</v>
+      </c>
+      <c r="I123" s="131" t="s">
+        <v>5175</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H124" s="131" t="s">
+        <v>5174</v>
+      </c>
+      <c r="I124" s="131" t="s">
+        <v>5175</v>
       </c>
     </row>
   </sheetData>
@@ -37496,7 +37613,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -38150,13 +38267,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3014</v>
+        <v>2966</v>
       </c>
       <c r="B35" t="s">
         <v>2967</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>3023</v>
+        <v>5160</v>
       </c>
       <c r="D35" t="s">
         <v>1264</v>
@@ -38170,19 +38287,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2966</v>
+        <v>3014</v>
       </c>
       <c r="B36" t="s">
         <v>2967</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="D36" t="s">
         <v>1264</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
       <c r="F36" t="s">
         <v>64</v>
@@ -38196,13 +38313,13 @@
         <v>2967</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="D37" t="s">
         <v>1264</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>4476</v>
+        <v>4477</v>
       </c>
       <c r="F37" t="s">
         <v>64</v>
@@ -38216,7 +38333,7 @@
         <v>2967</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="D38" t="s">
         <v>1264</v>
@@ -38230,39 +38347,39 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3027</v>
+        <v>2966</v>
       </c>
       <c r="B39" t="s">
         <v>2967</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>2030</v>
+        <v>3026</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1264</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>4478</v>
+        <v>4476</v>
       </c>
       <c r="F39" t="s">
-        <v>3028</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2966</v>
+        <v>3027</v>
       </c>
       <c r="B40" t="s">
         <v>2967</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>3029</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1256</v>
+        <v>2030</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -38273,13 +38390,13 @@
         <v>2967</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="D41" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E41" t="s">
-        <v>3031</v>
+        <v>1256</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>4479</v>
       </c>
       <c r="F41" t="s">
         <v>64</v>
@@ -38293,13 +38410,13 @@
         <v>2967</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="D42" t="s">
         <v>1254</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>4482</v>
+      <c r="E42" t="s">
+        <v>3031</v>
       </c>
       <c r="F42" t="s">
         <v>64</v>
@@ -38313,13 +38430,13 @@
         <v>2967</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="D43" t="s">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>4477</v>
+        <v>4482</v>
       </c>
       <c r="F43" t="s">
         <v>64</v>
@@ -38333,7 +38450,7 @@
         <v>2967</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="D44" t="s">
         <v>1264</v>
@@ -38353,13 +38470,13 @@
         <v>2967</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="D45" t="s">
         <v>1264</v>
       </c>
-      <c r="E45" t="s">
-        <v>3036</v>
+      <c r="E45" s="7" t="s">
+        <v>4477</v>
       </c>
       <c r="F45" t="s">
         <v>64</v>
@@ -38373,13 +38490,13 @@
         <v>2967</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="D46" t="s">
         <v>1264</v>
       </c>
       <c r="E46" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="F46" t="s">
         <v>64</v>
@@ -38393,13 +38510,13 @@
         <v>2967</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="D47" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="E47" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="F47" t="s">
         <v>64</v>
@@ -38413,13 +38530,13 @@
         <v>2967</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="D48" t="s">
-        <v>1240</v>
+        <v>1256</v>
       </c>
       <c r="E48" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="F48" t="s">
         <v>64</v>
@@ -38433,7 +38550,7 @@
         <v>2967</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="D49" t="s">
         <v>1240</v>
@@ -38453,7 +38570,7 @@
         <v>2967</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="D50" t="s">
         <v>1240</v>
@@ -38467,39 +38584,39 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3045</v>
+        <v>2966</v>
       </c>
       <c r="B51" t="s">
-        <v>3046</v>
+        <v>2967</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>3047</v>
+        <v>3044</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1240</v>
       </c>
       <c r="E51" t="s">
-        <v>3048</v>
+        <v>3042</v>
       </c>
       <c r="F51" t="s">
-        <v>3049</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2966</v>
+        <v>3045</v>
       </c>
       <c r="B52" t="s">
-        <v>2967</v>
+        <v>3046</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>3050</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1240</v>
+        <v>3047</v>
       </c>
       <c r="E52" t="s">
-        <v>3051</v>
+        <v>3048</v>
       </c>
       <c r="F52" t="s">
-        <v>2969</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -38510,33 +38627,33 @@
         <v>2967</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="D53" t="s">
         <v>1240</v>
       </c>
       <c r="E53" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="F53" t="s">
-        <v>3054</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3014</v>
+        <v>2966</v>
       </c>
       <c r="B54" t="s">
         <v>2967</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="D54" t="s">
         <v>1240</v>
       </c>
       <c r="E54" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="F54" t="s">
         <v>3054</v>
@@ -38544,22 +38661,22 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2966</v>
+        <v>3014</v>
       </c>
       <c r="B55" t="s">
         <v>2967</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="D55" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>4477</v>
+        <v>1240</v>
+      </c>
+      <c r="E55" t="s">
+        <v>3056</v>
       </c>
       <c r="F55" t="s">
-        <v>64</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -38570,13 +38687,13 @@
         <v>2967</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="D56" t="s">
         <v>1264</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>4476</v>
+        <v>4477</v>
       </c>
       <c r="F56" t="s">
         <v>64</v>
@@ -38584,7 +38701,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3014</v>
+        <v>2966</v>
       </c>
       <c r="B57" t="s">
         <v>2967</v>
@@ -38604,13 +38721,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2966</v>
+        <v>3014</v>
       </c>
       <c r="B58" t="s">
         <v>2967</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D58" t="s">
         <v>1264</v>
@@ -38630,19 +38747,19 @@
         <v>2967</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="D59" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E59" t="s">
-        <v>2994</v>
+        <v>1264</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>4476</v>
       </c>
       <c r="F59" t="s">
-        <v>2973</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>2966</v>
       </c>
@@ -38650,19 +38767,19 @@
         <v>2967</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="D60" t="s">
         <v>1240</v>
       </c>
-      <c r="E60" s="7" t="s">
-        <v>4483</v>
+      <c r="E60" t="s">
+        <v>2994</v>
       </c>
       <c r="F60" t="s">
-        <v>2988</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2966</v>
       </c>
@@ -38670,16 +38787,16 @@
         <v>2967</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="D61" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E61" t="s">
-        <v>3063</v>
+        <v>1240</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>4483</v>
       </c>
       <c r="F61" t="s">
-        <v>64</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -38690,13 +38807,13 @@
         <v>2967</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="D62" t="s">
         <v>1254</v>
       </c>
       <c r="E62" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="F62" t="s">
         <v>64</v>
@@ -38709,20 +38826,20 @@
       <c r="B63" t="s">
         <v>2967</v>
       </c>
-      <c r="C63" t="s">
-        <v>3066</v>
+      <c r="C63" s="12" t="s">
+        <v>3064</v>
       </c>
       <c r="D63" t="s">
-        <v>1240</v>
+        <v>1254</v>
       </c>
       <c r="E63" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="F63" t="s">
-        <v>3054</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2966</v>
       </c>
@@ -38730,19 +38847,19 @@
         <v>2967</v>
       </c>
       <c r="C64" t="s">
-        <v>4470</v>
+        <v>3066</v>
       </c>
       <c r="D64" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>4471</v>
-      </c>
-      <c r="F64" s="89" t="s">
-        <v>4472</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1240</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3067</v>
+      </c>
+      <c r="F64" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2966</v>
       </c>
@@ -38750,16 +38867,16 @@
         <v>2967</v>
       </c>
       <c r="C65" t="s">
-        <v>4501</v>
+        <v>4470</v>
       </c>
       <c r="D65" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E65" s="89" t="s">
-        <v>3051</v>
-      </c>
-      <c r="F65" s="91" t="s">
-        <v>64</v>
+        <v>1264</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>4471</v>
+      </c>
+      <c r="F65" s="89" t="s">
+        <v>4472</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -38770,7 +38887,7 @@
         <v>2967</v>
       </c>
       <c r="C66" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="D66" t="s">
         <v>1240</v>
@@ -38790,21 +38907,21 @@
         <v>2967</v>
       </c>
       <c r="C67" t="s">
-        <v>5068</v>
+        <v>4502</v>
       </c>
       <c r="D67" t="s">
-        <v>5069</v>
+        <v>1240</v>
       </c>
       <c r="E67" s="89" t="s">
-        <v>5070</v>
-      </c>
-      <c r="F67" t="s">
-        <v>5071</v>
+        <v>3051</v>
+      </c>
+      <c r="F67" s="91" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3014</v>
+        <v>2966</v>
       </c>
       <c r="B68" t="s">
         <v>2967</v>
@@ -38824,19 +38941,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2966</v>
+        <v>3014</v>
       </c>
       <c r="B69" t="s">
         <v>2967</v>
       </c>
       <c r="C69" t="s">
-        <v>5083</v>
+        <v>5068</v>
       </c>
       <c r="D69" t="s">
         <v>5069</v>
       </c>
       <c r="E69" s="89" t="s">
-        <v>5084</v>
+        <v>5070</v>
       </c>
       <c r="F69" t="s">
         <v>5071</v>
@@ -38844,7 +38961,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3014</v>
+        <v>2966</v>
       </c>
       <c r="B70" t="s">
         <v>2967</v>
@@ -38870,26 +38987,49 @@
         <v>2967</v>
       </c>
       <c r="C71" t="s">
-        <v>5085</v>
+        <v>5083</v>
       </c>
       <c r="D71" t="s">
         <v>5069</v>
       </c>
       <c r="E71" s="89" t="s">
+        <v>5084</v>
+      </c>
+      <c r="F71" t="s">
+        <v>5071</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>3014</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5085</v>
+      </c>
+      <c r="D72" t="s">
+        <v>5069</v>
+      </c>
+      <c r="E72" s="89" t="s">
         <v>5086</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C64 C3:C62 C67:C70 C72:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="C65 C3:C34 C68:C71 C73:C1048576 C36:C63">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32 C52 C4:C18 E52 C54:C55 C67:C70 C72:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="103"/>
+  <conditionalFormatting sqref="C53 C32 C4:C18 E53 C55:C56 C68:C71 C73:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C67">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C65:C66">
+  <conditionalFormatting sqref="C35">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
@@ -55759,7 +55899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E1143"/>
+  <dimension ref="A1:E1151"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" style="3" customWidth="1"/>
@@ -59348,9 +59488,6 @@
         <v>434</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" s="12"/>
-    </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="12" t="s">
         <v>776</v>
@@ -60089,30 +60226,30 @@
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400" s="12" t="s">
-        <v>839</v>
+      <c r="A400" t="s">
+        <v>5161</v>
       </c>
       <c r="B400" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C400" t="s">
-        <v>439</v>
+        <v>764</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" s="12" t="s">
-        <v>840</v>
+      <c r="A401" t="s">
+        <v>5162</v>
       </c>
       <c r="B401" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C401" t="s">
-        <v>439</v>
+        <v>764</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="12" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B402" t="s">
         <v>335</v>
@@ -60123,7 +60260,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="12" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B403" t="s">
         <v>335</v>
@@ -60134,31 +60271,47 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="12" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B404" t="s">
         <v>335</v>
       </c>
       <c r="C404" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="12" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B405" t="s">
         <v>335</v>
       </c>
       <c r="C405" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="B406" t="s">
+        <v>335</v>
+      </c>
+      <c r="C406" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="12"/>
-    </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" s="12"/>
+      <c r="A407" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="B407" t="s">
+        <v>335</v>
+      </c>
+      <c r="C407" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="12"/>
@@ -60167,30 +60320,14 @@
       <c r="A409" s="12"/>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" s="12" t="s">
-        <v>845</v>
-      </c>
-      <c r="B410" t="s">
-        <v>335</v>
-      </c>
-      <c r="C410" t="s">
-        <v>764</v>
-      </c>
+      <c r="A410" s="12"/>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="B411" t="s">
-        <v>335</v>
-      </c>
-      <c r="C411" t="s">
-        <v>764</v>
-      </c>
+      <c r="A411" s="12"/>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="12" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B412" t="s">
         <v>335</v>
@@ -60200,64 +60337,72 @@
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413" s="12"/>
+      <c r="A413" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="B413" t="s">
+        <v>335</v>
+      </c>
+      <c r="C413" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A414" s="12"/>
+      <c r="A414" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="B414" t="s">
+        <v>335</v>
+      </c>
+      <c r="C414" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="B415" t="s">
-        <v>475</v>
-      </c>
-      <c r="C415" t="s">
-        <v>771</v>
-      </c>
+      <c r="A415" s="12"/>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" s="12" t="s">
-        <v>849</v>
-      </c>
-      <c r="B416" t="s">
-        <v>335</v>
-      </c>
-      <c r="C416" t="s">
-        <v>764</v>
-      </c>
+      <c r="A416" s="12"/>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="12" t="s">
-        <v>5026</v>
+        <v>848</v>
       </c>
       <c r="B417" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="C417" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="12" t="s">
-        <v>5144</v>
+        <v>849</v>
       </c>
       <c r="B418" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C418" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A419" s="12"/>
+      <c r="A419" s="12" t="s">
+        <v>5026</v>
+      </c>
+      <c r="B419" t="s">
+        <v>331</v>
+      </c>
+      <c r="C419" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="12" t="s">
-        <v>850</v>
+        <v>5144</v>
       </c>
       <c r="B420" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C420" t="s">
         <v>764</v>
@@ -60265,10 +60410,10 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="12" t="s">
-        <v>851</v>
+        <v>5166</v>
       </c>
       <c r="B421" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C421" t="s">
         <v>764</v>
@@ -60276,68 +60421,68 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="12" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B422" t="s">
         <v>335</v>
       </c>
       <c r="C422" t="s">
-        <v>329</v>
+        <v>764</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423" s="12"/>
+      <c r="A423" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="B423" t="s">
+        <v>335</v>
+      </c>
+      <c r="C423" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B424" t="s">
         <v>335</v>
       </c>
       <c r="C424" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" s="12"/>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="B426" t="s">
+        <v>335</v>
+      </c>
+      <c r="C426" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425" s="12" t="s">
-        <v>855</v>
-      </c>
-      <c r="B425" t="s">
-        <v>335</v>
-      </c>
-      <c r="C425" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" s="12"/>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="12" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B427" t="s">
         <v>335</v>
       </c>
       <c r="C427" t="s">
-        <v>764</v>
+        <v>329</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428" s="12" t="s">
-        <v>857</v>
-      </c>
-      <c r="B428" t="s">
-        <v>335</v>
-      </c>
-      <c r="C428" t="s">
-        <v>764</v>
-      </c>
+      <c r="A428" s="12"/>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="12" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B429" t="s">
         <v>335</v>
@@ -60348,7 +60493,7 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="12" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B430" t="s">
         <v>335</v>
@@ -60359,18 +60504,18 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="12" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B431" t="s">
         <v>335</v>
       </c>
       <c r="C431" t="s">
-        <v>329</v>
+        <v>764</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="12" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B432" t="s">
         <v>335</v>
@@ -60379,20 +60524,20 @@
         <v>764</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="12" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B433" t="s">
         <v>335</v>
       </c>
       <c r="C433" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B434" t="s">
         <v>335</v>
@@ -60401,20 +60546,20 @@
         <v>764</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="12" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B435" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C435" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="12" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B436" t="s">
         <v>335</v>
@@ -60423,20 +60568,20 @@
         <v>764</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B437" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C437" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="12" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B438" t="s">
         <v>335</v>
@@ -60445,9 +60590,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="12" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B439" t="s">
         <v>335</v>
@@ -60456,9 +60601,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="12" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B440" t="s">
         <v>335</v>
@@ -60467,9 +60612,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="12" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B441" t="s">
         <v>335</v>
@@ -60478,9 +60623,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="12" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B442" t="s">
         <v>335</v>
@@ -60489,23 +60634,31 @@
         <v>764</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A443" s="12"/>
-    </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="B443" t="s">
+        <v>335</v>
+      </c>
+      <c r="C443" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B444" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C444" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="12" t="s">
-        <v>873</v>
+        <v>5167</v>
       </c>
       <c r="B445" t="s">
         <v>331</v>
@@ -60514,9 +60667,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="12" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B446" t="s">
         <v>331</v>
@@ -60525,9 +60678,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A447" s="117" t="s">
-        <v>5002</v>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" s="12" t="s">
+        <v>873</v>
       </c>
       <c r="B447" t="s">
         <v>331</v>
@@ -60535,11 +60688,10 @@
       <c r="C447" t="s">
         <v>764</v>
       </c>
-      <c r="D447" s="116"/>
-    </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B448" t="s">
         <v>331</v>
@@ -60548,9 +60700,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A449" s="12" t="s">
-        <v>876</v>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449" s="117" t="s">
+        <v>5002</v>
       </c>
       <c r="B449" t="s">
         <v>331</v>
@@ -60558,10 +60710,11 @@
       <c r="C449" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D449" s="116"/>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" s="12" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B450" t="s">
         <v>331</v>
@@ -60570,9 +60723,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" s="12" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B451" t="s">
         <v>331</v>
@@ -60581,9 +60734,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" s="12" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B452" t="s">
         <v>331</v>
@@ -60592,9 +60745,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" s="12" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B453" t="s">
         <v>331</v>
@@ -60603,9 +60756,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="12" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B454" t="s">
         <v>331</v>
@@ -60614,9 +60767,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" s="12" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B455" t="s">
         <v>331</v>
@@ -60625,9 +60778,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" s="12" t="s">
-        <v>4443</v>
+        <v>881</v>
       </c>
       <c r="B456" t="s">
         <v>331</v>
@@ -60636,9 +60789,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" s="12" t="s">
-        <v>4473</v>
+        <v>882</v>
       </c>
       <c r="B457" t="s">
         <v>331</v>
@@ -60647,9 +60800,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" s="12" t="s">
-        <v>4490</v>
+        <v>4443</v>
       </c>
       <c r="B458" t="s">
         <v>331</v>
@@ -60658,155 +60811,131 @@
         <v>764</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" s="12" t="s">
-        <v>883</v>
+        <v>4473</v>
       </c>
       <c r="B459" t="s">
-        <v>475</v>
+        <v>331</v>
       </c>
       <c r="C459" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" s="12"/>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460" s="12" t="s">
+        <v>4490</v>
+      </c>
+      <c r="B460" t="s">
+        <v>331</v>
+      </c>
+      <c r="C460" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" s="12" t="s">
-        <v>4337</v>
+        <v>5168</v>
       </c>
       <c r="B461" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C461" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" s="12" t="s">
-        <v>4338</v>
+        <v>764</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>5169</v>
       </c>
       <c r="B462" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C462" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" s="12" t="s">
-        <v>4339</v>
+        <v>5170</v>
       </c>
       <c r="B463" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C463" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464" s="12" t="s">
-        <v>5093</v>
-      </c>
-      <c r="B464" t="s">
-        <v>331</v>
-      </c>
-      <c r="C464" t="s">
         <v>764</v>
       </c>
     </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464" s="12"/>
+    </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A465" s="12" t="s">
-        <v>4341</v>
-      </c>
-      <c r="B465" t="s">
-        <v>331</v>
-      </c>
-      <c r="C465" t="s">
-        <v>764</v>
-      </c>
+      <c r="A465" s="12"/>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" s="12" t="s">
-        <v>4342</v>
-      </c>
-      <c r="B466" t="s">
-        <v>331</v>
-      </c>
-      <c r="C466" t="s">
-        <v>487</v>
-      </c>
+      <c r="A466" s="12"/>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="12" t="s">
-        <v>4343</v>
+        <v>883</v>
       </c>
       <c r="B467" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="C467" t="s">
-        <v>487</v>
+        <v>771</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" s="12" t="s">
-        <v>4344</v>
-      </c>
-      <c r="B468" t="s">
-        <v>331</v>
-      </c>
-      <c r="C468" t="s">
-        <v>764</v>
-      </c>
+      <c r="A468" s="12"/>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="12" t="s">
-        <v>4345</v>
+        <v>4337</v>
       </c>
       <c r="B469" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C469" t="s">
-        <v>487</v>
+        <v>439</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="12" t="s">
-        <v>4346</v>
+        <v>4338</v>
       </c>
       <c r="B470" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C470" t="s">
-        <v>487</v>
+        <v>439</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="12" t="s">
-        <v>4347</v>
+        <v>4339</v>
       </c>
       <c r="B471" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C471" t="s">
-        <v>487</v>
+        <v>439</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="12" t="s">
-        <v>4348</v>
+        <v>5093</v>
       </c>
       <c r="B472" t="s">
         <v>331</v>
       </c>
       <c r="C472" t="s">
-        <v>487</v>
+        <v>764</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="12" t="s">
-        <v>4349</v>
+        <v>4341</v>
       </c>
       <c r="B473" t="s">
         <v>331</v>
@@ -60817,7 +60946,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="12" t="s">
-        <v>4350</v>
+        <v>4342</v>
       </c>
       <c r="B474" t="s">
         <v>331</v>
@@ -60828,7 +60957,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="12" t="s">
-        <v>4351</v>
+        <v>4343</v>
       </c>
       <c r="B475" t="s">
         <v>331</v>
@@ -60839,18 +60968,18 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="12" t="s">
-        <v>4352</v>
+        <v>4344</v>
       </c>
       <c r="B476" t="s">
         <v>331</v>
       </c>
       <c r="C476" t="s">
-        <v>487</v>
+        <v>764</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="12" t="s">
-        <v>4353</v>
+        <v>4345</v>
       </c>
       <c r="B477" t="s">
         <v>331</v>
@@ -60860,62 +60989,126 @@
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478" s="13"/>
+      <c r="A478" s="12" t="s">
+        <v>4346</v>
+      </c>
+      <c r="B478" t="s">
+        <v>331</v>
+      </c>
+      <c r="C478" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479" s="3" t="s">
+      <c r="A479" s="12" t="s">
+        <v>4347</v>
+      </c>
+      <c r="B479" t="s">
+        <v>331</v>
+      </c>
+      <c r="C479" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" s="12" t="s">
+        <v>4348</v>
+      </c>
+      <c r="B480" t="s">
+        <v>331</v>
+      </c>
+      <c r="C480" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" s="12" t="s">
+        <v>4349</v>
+      </c>
+      <c r="B481" t="s">
+        <v>331</v>
+      </c>
+      <c r="C481" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" s="12" t="s">
+        <v>4350</v>
+      </c>
+      <c r="B482" t="s">
+        <v>331</v>
+      </c>
+      <c r="C482" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" s="12" t="s">
+        <v>4351</v>
+      </c>
+      <c r="B483" t="s">
+        <v>331</v>
+      </c>
+      <c r="C483" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" s="12" t="s">
+        <v>4352</v>
+      </c>
+      <c r="B484" t="s">
+        <v>331</v>
+      </c>
+      <c r="C484" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" s="12" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B485" t="s">
+        <v>331</v>
+      </c>
+      <c r="C485" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" s="13"/>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" s="3" t="s">
         <v>4833</v>
       </c>
-      <c r="B479" t="s">
+      <c r="B487" t="s">
         <v>335</v>
       </c>
-      <c r="C479" t="s">
+      <c r="C487" t="s">
         <v>4832</v>
       </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A481" s="13"/>
-    </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A483" s="13"/>
-    </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A484" s="13"/>
-    </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A485" s="13"/>
-    </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A486" s="13"/>
-    </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A487" s="13"/>
-    </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A488" s="13"/>
-    </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="13"/>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A490" s="13"/>
-    </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="13"/>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="13"/>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="13"/>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="13"/>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="13"/>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="13"/>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.25">
@@ -62859,62 +63052,86 @@
     <row r="1143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1143" s="13"/>
     </row>
+    <row r="1144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1144" s="13"/>
+    </row>
+    <row r="1145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1145" s="13"/>
+    </row>
+    <row r="1146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1146" s="13"/>
+    </row>
+    <row r="1147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1147" s="13"/>
+    </row>
+    <row r="1148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1148" s="13"/>
+    </row>
+    <row r="1149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1149" s="13"/>
+    </row>
+    <row r="1150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1150" s="13"/>
+    </row>
+    <row r="1151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1151" s="13"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1144:A1048576 A3:A8 A64:A115 A171:A177 A198:A208 A211:A214 A43:A61 A10:A17 A179:A196 A216:A229 A19:A41">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+  <conditionalFormatting sqref="A1152:A1048576 A3:A8 A64:A115 A171:A177 A198:A208 A211:A214 A43:A61 A10:A17 A179:A196 A216:A229 A19:A41">
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A197">
-    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A144:A155 A170">
-    <cfRule type="duplicateValues" dxfId="29" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116:A123 A125:A128">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116:A123 A125:A128">
-    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A156:A161 A166:A169">
-    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="24" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A478:A479 A481 A483:A1048576 D447 A447 A328:A330 A3:A8 A210:A214 A43:A115 A171:A208 A216:A282 A162:A165 E124 A10:A41 A286:A320">
-    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="34"/>
+  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A328:A330 A3:A8 A210:A214 A43:A115 A171:A208 A216:A282 A162:A165 E124 A10:A41 A286:A320">
+    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A478:A479 A481 A483:A1048576 D447 A447 A328:A330 A3:A8 A43:A115 A129:A143 A171:A282 A162:A165 E124 A10:A41 A286:A320">
-    <cfRule type="duplicateValues" dxfId="21" priority="35"/>
+  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A328:A330 A3:A8 A43:A115 A129:A143 A171:A282 A162:A165 E124 A10:A41 A286:A320">
+    <cfRule type="duplicateValues" dxfId="22" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A478:A479 A481 A483:A1048576 D447 A447 A327:A332 A162:A165 E124 A125:A155 A3:A123 A170:A324">
-    <cfRule type="duplicateValues" dxfId="20" priority="36"/>
+  <conditionalFormatting sqref="A486:A487 A286 A489 A491:A1048576 D449 A449">
+    <cfRule type="duplicateValues" dxfId="21" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A478:A479 A286 A481 A483:A1048576 D447 A447">
-    <cfRule type="duplicateValues" dxfId="19" priority="37"/>
+  <conditionalFormatting sqref="A333:A397 A450:A453 A402:A420 A422:A448 A399">
+    <cfRule type="duplicateValues" dxfId="20" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A478:A479 A481 A483:A1048576 D447 A447 A327:A332 A3:A324">
-    <cfRule type="duplicateValues" dxfId="18" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="40"/>
+  <conditionalFormatting sqref="A333:A397 A450:A453 A402:A420 A422:A448 A399">
+    <cfRule type="duplicateValues" dxfId="18" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A333:A397 A448:A451 A399:A446">
-    <cfRule type="duplicateValues" dxfId="16" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="98"/>
+  <conditionalFormatting sqref="A454:A461 A463:A485">
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A333:A397 A448:A451 A399:A446">
-    <cfRule type="duplicateValues" dxfId="14" priority="101"/>
+  <conditionalFormatting sqref="A454:A461 A463:A485">
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A452:A477">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+  <conditionalFormatting sqref="A489:A1048576 A1:A331 A333:A397 A402:A461 A463:A487 A399">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A452:A477">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A327:A331 A421 A162:A165 E124 A125:A155 A3:A123 A170:A324">
+    <cfRule type="duplicateValues" dxfId="13" priority="160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A481:A1048576 A1:A397 A399:A479">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A327:A331 A421 A3:A324">
+    <cfRule type="duplicateValues" dxfId="12" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="179"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -64057,7 +64274,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{8EA37169-2323-40C3-9046-4C9A4C68151F}"/>

--- a/san_automation_info.xlsx
+++ b/san_automation_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\05.PYTHON\Projects\san_report_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FEF7DE-4A2E-43A5-8114-B8F9D560239F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1186FF7C-AFE9-4CFC-AAE3-EB1B6540966C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" firstSheet="5" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contents" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11826" uniqueCount="5177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11829" uniqueCount="5178">
   <si>
     <t>Contents</t>
   </si>
@@ -16382,6 +16382,9 @@
   </si>
   <si>
     <t>flow sid did un(quarantined)</t>
+  </si>
+  <si>
+    <t>e1:11:c2</t>
   </si>
 </sst>
 </file>
@@ -55899,7 +55902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E1151"/>
+  <dimension ref="A1:E1152"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" style="3" customWidth="1"/>
@@ -58247,29 +58250,29 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>657</v>
+        <v>5177</v>
       </c>
       <c r="B219" t="s">
         <v>333</v>
       </c>
       <c r="C219" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B220" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C220" t="s">
-        <v>550</v>
+        <v>658</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B221" t="s">
         <v>331</v>
@@ -58280,106 +58283,106 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B222" t="s">
+        <v>331</v>
+      </c>
+      <c r="C222" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="B222" t="s">
-        <v>335</v>
-      </c>
-      <c r="C222" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="17" t="s">
-        <v>662</v>
       </c>
       <c r="B223" t="s">
         <v>335</v>
       </c>
       <c r="C223" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="B224" t="s">
+        <v>335</v>
+      </c>
+      <c r="C224" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="19" t="s">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="19" t="s">
         <v>663</v>
       </c>
-      <c r="B224" s="20" t="s">
+      <c r="B225" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="C224" s="20" t="s">
+      <c r="C225" s="20" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="3" t="s">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B226" t="s">
         <v>333</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C226" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="12" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="12" t="s">
         <v>667</v>
-      </c>
-      <c r="B226" t="s">
-        <v>335</v>
-      </c>
-      <c r="C226" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="B227" t="s">
         <v>335</v>
       </c>
       <c r="C227" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B228" t="s">
         <v>335</v>
       </c>
       <c r="C228" t="s">
-        <v>670</v>
+        <v>434</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B229" t="s">
         <v>335</v>
       </c>
       <c r="C229" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B230" t="s">
+        <v>335</v>
+      </c>
+      <c r="C230" t="s">
         <v>437</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="12" t="s">
-        <v>672</v>
-      </c>
-      <c r="B230" t="s">
-        <v>409</v>
-      </c>
-      <c r="C230" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B231" t="s">
         <v>409</v>
@@ -58390,7 +58393,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B232" t="s">
         <v>409</v>
@@ -58401,7 +58404,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B233" t="s">
         <v>409</v>
@@ -58412,7 +58415,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B234" t="s">
         <v>409</v>
@@ -58423,7 +58426,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B235" t="s">
         <v>409</v>
@@ -58434,10 +58437,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B236" t="s">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="C236" t="s">
         <v>673</v>
@@ -58445,84 +58448,84 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B237" t="s">
         <v>335</v>
       </c>
       <c r="C237" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>4489</v>
+        <v>680</v>
       </c>
       <c r="B238" t="s">
         <v>335</v>
       </c>
       <c r="C238" t="s">
-        <v>329</v>
+        <v>681</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
-        <v>682</v>
+        <v>4489</v>
       </c>
       <c r="B239" t="s">
         <v>335</v>
       </c>
       <c r="C239" t="s">
-        <v>683</v>
+        <v>329</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="13" t="s">
-        <v>684</v>
+      <c r="A240" s="12" t="s">
+        <v>682</v>
       </c>
       <c r="B240" t="s">
         <v>335</v>
       </c>
       <c r="C240" t="s">
-        <v>437</v>
+        <v>683</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B241" t="s">
         <v>335</v>
       </c>
       <c r="C241" t="s">
-        <v>621</v>
+        <v>437</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B242" t="s">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="C242" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="12" t="s">
-        <v>687</v>
+      <c r="A243" s="13" t="s">
+        <v>686</v>
       </c>
       <c r="B243" t="s">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="C243" t="s">
-        <v>688</v>
+        <v>621</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B244" t="s">
         <v>335</v>
@@ -58533,21 +58536,21 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="B245" t="s">
+        <v>335</v>
+      </c>
+      <c r="C245" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B246" t="s">
         <v>409</v>
-      </c>
-      <c r="C245" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="13" t="s">
-        <v>691</v>
-      </c>
-      <c r="B246" t="s">
-        <v>331</v>
       </c>
       <c r="C246" t="s">
         <v>621</v>
@@ -58555,62 +58558,62 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="B247" t="s">
+        <v>331</v>
+      </c>
+      <c r="C247" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="13" t="s">
         <v>692</v>
-      </c>
-      <c r="B247" t="s">
-        <v>335</v>
-      </c>
-      <c r="C247" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="17" t="s">
-        <v>693</v>
       </c>
       <c r="B248" t="s">
         <v>335</v>
       </c>
       <c r="C248" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="B249" t="s">
+        <v>335</v>
+      </c>
+      <c r="C249" t="s">
         <v>437</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="12" t="s">
-        <v>694</v>
-      </c>
-      <c r="B249" t="s">
-        <v>333</v>
-      </c>
-      <c r="C249" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B250" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C250" t="s">
-        <v>467</v>
+        <v>429</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B251" t="s">
         <v>335</v>
       </c>
       <c r="C251" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B252" t="s">
         <v>335</v>
@@ -58621,7 +58624,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B253" t="s">
         <v>335</v>
@@ -58632,7 +58635,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B254" t="s">
         <v>335</v>
@@ -58643,7 +58646,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B255" t="s">
         <v>335</v>
@@ -58654,7 +58657,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B256" t="s">
         <v>335</v>
@@ -58665,40 +58668,40 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B257" t="s">
         <v>335</v>
       </c>
       <c r="C257" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B258" t="s">
         <v>335</v>
       </c>
       <c r="C258" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B259" t="s">
         <v>335</v>
       </c>
       <c r="C259" t="s">
-        <v>329</v>
+        <v>439</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B260" t="s">
         <v>335</v>
@@ -58709,7 +58712,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B261" t="s">
         <v>335</v>
@@ -58720,7 +58723,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B262" t="s">
         <v>335</v>
@@ -58731,7 +58734,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B263" t="s">
         <v>335</v>
@@ -58742,7 +58745,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B264" t="s">
         <v>335</v>
@@ -58753,7 +58756,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B265" t="s">
         <v>335</v>
@@ -58764,7 +58767,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B266" t="s">
         <v>335</v>
@@ -58775,7 +58778,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B267" t="s">
         <v>335</v>
@@ -58786,7 +58789,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B268" t="s">
         <v>335</v>
@@ -58797,7 +58800,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B269" t="s">
         <v>335</v>
@@ -58808,7 +58811,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B270" t="s">
         <v>335</v>
@@ -58819,7 +58822,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="12" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B271" t="s">
         <v>335</v>
@@ -58830,7 +58833,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B272" t="s">
         <v>335</v>
@@ -58841,7 +58844,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B273" t="s">
         <v>335</v>
@@ -58852,7 +58855,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B274" t="s">
         <v>335</v>
@@ -58863,7 +58866,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B275" t="s">
         <v>335</v>
@@ -58874,7 +58877,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B276" t="s">
         <v>335</v>
@@ -58885,7 +58888,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B277" t="s">
         <v>335</v>
@@ -58896,7 +58899,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B278" t="s">
         <v>335</v>
@@ -58907,7 +58910,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B279" t="s">
         <v>335</v>
@@ -58918,7 +58921,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B280" t="s">
         <v>335</v>
@@ -58928,8 +58931,8 @@
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="13" t="s">
-        <v>726</v>
+      <c r="A281" s="12" t="s">
+        <v>725</v>
       </c>
       <c r="B281" t="s">
         <v>335</v>
@@ -58940,7 +58943,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B282" t="s">
         <v>335</v>
@@ -58950,8 +58953,8 @@
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="12" t="s">
-        <v>728</v>
+      <c r="A283" s="13" t="s">
+        <v>727</v>
       </c>
       <c r="B283" t="s">
         <v>335</v>
@@ -58962,7 +58965,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B284" t="s">
         <v>335</v>
@@ -58973,7 +58976,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B285" t="s">
         <v>335</v>
@@ -58984,7 +58987,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>5141</v>
+        <v>730</v>
       </c>
       <c r="B286" t="s">
         <v>335</v>
@@ -58995,29 +58998,29 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="12" t="s">
-        <v>731</v>
+        <v>5141</v>
       </c>
       <c r="B287" t="s">
         <v>335</v>
       </c>
       <c r="C287" t="s">
-        <v>437</v>
+        <v>329</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B288" t="s">
         <v>335</v>
       </c>
       <c r="C288" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B289" t="s">
         <v>335</v>
@@ -59028,7 +59031,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B290" t="s">
         <v>335</v>
@@ -59039,7 +59042,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B291" t="s">
         <v>335</v>
@@ -59050,18 +59053,18 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B292" t="s">
         <v>335</v>
       </c>
       <c r="C292" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B293" t="s">
         <v>335</v>
@@ -59072,18 +59075,18 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B294" t="s">
         <v>335</v>
       </c>
       <c r="C294" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="12" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B295" t="s">
         <v>335</v>
@@ -59094,18 +59097,18 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B296" t="s">
         <v>335</v>
       </c>
       <c r="C296" t="s">
-        <v>329</v>
+        <v>439</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="12" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B297" t="s">
         <v>335</v>
@@ -59116,29 +59119,29 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B298" t="s">
-        <v>431</v>
+        <v>335</v>
       </c>
       <c r="C298" t="s">
-        <v>743</v>
+        <v>329</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="12" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B299" t="s">
-        <v>333</v>
+        <v>431</v>
       </c>
       <c r="C299" t="s">
-        <v>645</v>
+        <v>743</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B300" t="s">
         <v>333</v>
@@ -59149,7 +59152,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B301" t="s">
         <v>333</v>
@@ -59160,18 +59163,18 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="12" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B302" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C302" t="s">
-        <v>748</v>
+        <v>645</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="12" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B303" t="s">
         <v>331</v>
@@ -59182,7 +59185,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="12" t="s">
-        <v>4488</v>
+        <v>749</v>
       </c>
       <c r="B304" t="s">
         <v>331</v>
@@ -59193,29 +59196,29 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="12" t="s">
-        <v>750</v>
+        <v>4488</v>
       </c>
       <c r="B305" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C305" t="s">
-        <v>329</v>
+        <v>748</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="12" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B306" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C306" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="12" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B307" t="s">
         <v>331</v>
@@ -59226,51 +59229,51 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="B308" t="s">
+        <v>331</v>
+      </c>
+      <c r="C308" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B309" t="s">
         <v>335</v>
       </c>
-      <c r="C308" t="s">
+      <c r="C309" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="13" t="s">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="13" t="s">
         <v>755</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B310" t="s">
         <v>331</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C310" t="s">
         <v>748</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="12" t="s">
-        <v>756</v>
-      </c>
-      <c r="B310" t="s">
-        <v>431</v>
-      </c>
-      <c r="C310" t="s">
-        <v>4340</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B311" t="s">
-        <v>331</v>
+        <v>431</v>
       </c>
       <c r="C311" t="s">
-        <v>487</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B312" t="s">
         <v>331</v>
@@ -59281,7 +59284,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B313" t="s">
         <v>331</v>
@@ -59292,7 +59295,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B314" t="s">
         <v>331</v>
@@ -59303,7 +59306,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B315" t="s">
         <v>331</v>
@@ -59314,7 +59317,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B316" t="s">
         <v>331</v>
@@ -59325,7 +59328,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="12" t="s">
-        <v>4497</v>
+        <v>762</v>
       </c>
       <c r="B317" t="s">
         <v>331</v>
@@ -59336,7 +59339,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="12" t="s">
-        <v>4496</v>
+        <v>4497</v>
       </c>
       <c r="B318" t="s">
         <v>331</v>
@@ -59347,18 +59350,18 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="12" t="s">
-        <v>763</v>
+        <v>4496</v>
       </c>
       <c r="B319" t="s">
         <v>331</v>
       </c>
       <c r="C319" t="s">
-        <v>764</v>
+        <v>487</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="12" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B320" t="s">
         <v>331</v>
@@ -59369,7 +59372,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="12" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B321" t="s">
         <v>331</v>
@@ -59380,7 +59383,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B322" t="s">
         <v>331</v>
@@ -59391,7 +59394,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B323" t="s">
         <v>331</v>
@@ -59402,7 +59405,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B324" t="s">
         <v>331</v>
@@ -59412,8 +59415,8 @@
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>4438</v>
+      <c r="A325" s="12" t="s">
+        <v>769</v>
       </c>
       <c r="B325" t="s">
         <v>331</v>
@@ -59424,7 +59427,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>4439</v>
+        <v>4438</v>
       </c>
       <c r="B326" t="s">
         <v>331</v>
@@ -59434,41 +59437,41 @@
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" s="12" t="s">
-        <v>770</v>
+      <c r="A327" t="s">
+        <v>4439</v>
       </c>
       <c r="B327" t="s">
-        <v>475</v>
+        <v>331</v>
       </c>
       <c r="C327" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="12" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B328" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="C328" t="s">
-        <v>598</v>
+        <v>771</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B329" t="s">
         <v>331</v>
       </c>
       <c r="C329" t="s">
-        <v>417</v>
+        <v>598</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="12" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B330" t="s">
         <v>331</v>
@@ -59479,32 +59482,32 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="B331" t="s">
+        <v>331</v>
+      </c>
+      <c r="C331" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B332" t="s">
         <v>335</v>
       </c>
-      <c r="C331" t="s">
+      <c r="C332" t="s">
         <v>434</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" s="12" t="s">
-        <v>776</v>
-      </c>
-      <c r="B333" t="s">
-        <v>409</v>
-      </c>
-      <c r="C333" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="12" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B334" t="s">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="C334" t="s">
         <v>764</v>
@@ -59512,7 +59515,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B335" t="s">
         <v>335</v>
@@ -59523,7 +59526,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="12" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B336" t="s">
         <v>335</v>
@@ -59534,7 +59537,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B337" t="s">
         <v>335</v>
@@ -59545,7 +59548,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B338" t="s">
         <v>335</v>
@@ -59556,7 +59559,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="12" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B339" t="s">
         <v>335</v>
@@ -59567,7 +59570,7 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B340" t="s">
         <v>335</v>
@@ -59578,7 +59581,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="12" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B341" t="s">
         <v>335</v>
@@ -59589,62 +59592,62 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B342" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C342" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B343" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C343" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="12" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B344" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C344" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="12" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B345" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C345" t="s">
-        <v>439</v>
+        <v>771</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B346" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C346" t="s">
-        <v>764</v>
+        <v>439</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="12" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B347" t="s">
         <v>331</v>
@@ -59655,29 +59658,29 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="12" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B348" t="s">
-        <v>475</v>
+        <v>331</v>
       </c>
       <c r="C348" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B349" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C349" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B350" t="s">
         <v>335</v>
@@ -59688,7 +59691,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B351" t="s">
         <v>335</v>
@@ -59699,7 +59702,7 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="12" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B352" t="s">
         <v>335</v>
@@ -59710,7 +59713,7 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="12" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B353" t="s">
         <v>335</v>
@@ -59721,7 +59724,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="12" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B354" t="s">
         <v>335</v>
@@ -59732,7 +59735,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="12" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B355" t="s">
         <v>335</v>
@@ -59743,7 +59746,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B356" t="s">
         <v>335</v>
@@ -59754,29 +59757,29 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B357" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C357" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B358" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C358" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B359" t="s">
         <v>335</v>
@@ -59787,7 +59790,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B360" t="s">
         <v>335</v>
@@ -59798,7 +59801,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B361" t="s">
         <v>335</v>
@@ -59809,7 +59812,7 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B362" t="s">
         <v>335</v>
@@ -59820,7 +59823,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B363" t="s">
         <v>335</v>
@@ -59831,7 +59834,7 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B364" t="s">
         <v>335</v>
@@ -59842,7 +59845,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B365" t="s">
         <v>335</v>
@@ -59853,29 +59856,29 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B366" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C366" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B367" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C367" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B368" t="s">
         <v>335</v>
@@ -59886,7 +59889,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B369" t="s">
         <v>335</v>
@@ -59897,7 +59900,7 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="12" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B370" t="s">
         <v>335</v>
@@ -59908,29 +59911,29 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B371" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C371" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B372" t="s">
-        <v>331</v>
+        <v>475</v>
       </c>
       <c r="C372" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B373" t="s">
         <v>331</v>
@@ -59941,7 +59944,7 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B374" t="s">
         <v>331</v>
@@ -59952,7 +59955,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B375" t="s">
         <v>331</v>
@@ -59963,7 +59966,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B376" t="s">
         <v>331</v>
@@ -59974,10 +59977,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B377" t="s">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="C377" t="s">
         <v>764</v>
@@ -59985,10 +59988,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="12" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B378" t="s">
-        <v>472</v>
+        <v>409</v>
       </c>
       <c r="C378" t="s">
         <v>764</v>
@@ -59996,7 +59999,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B379" t="s">
         <v>472</v>
@@ -60007,7 +60010,7 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B380" t="s">
         <v>472</v>
@@ -60018,10 +60021,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B381" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="C381" t="s">
         <v>764</v>
@@ -60029,7 +60032,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B382" t="s">
         <v>409</v>
@@ -60040,10 +60043,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B383" t="s">
-        <v>827</v>
+        <v>409</v>
       </c>
       <c r="C383" t="s">
         <v>764</v>
@@ -60051,10 +60054,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="12" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B384" t="s">
-        <v>409</v>
+        <v>827</v>
       </c>
       <c r="C384" t="s">
         <v>764</v>
@@ -60062,10 +60065,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B385" t="s">
-        <v>827</v>
+        <v>409</v>
       </c>
       <c r="C385" t="s">
         <v>764</v>
@@ -60073,10 +60076,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B386" t="s">
-        <v>472</v>
+        <v>827</v>
       </c>
       <c r="C386" t="s">
         <v>764</v>
@@ -60084,10 +60087,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="12" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B387" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="C387" t="s">
         <v>764</v>
@@ -60095,7 +60098,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="12" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B388" t="s">
         <v>409</v>
@@ -60106,10 +60109,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B389" t="s">
-        <v>472</v>
+        <v>409</v>
       </c>
       <c r="C389" t="s">
         <v>764</v>
@@ -60117,7 +60120,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B390" t="s">
         <v>472</v>
@@ -60128,10 +60131,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B391" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="C391" t="s">
         <v>764</v>
@@ -60139,7 +60142,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="12" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B392" t="s">
         <v>409</v>
@@ -60150,10 +60153,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="12" t="s">
-        <v>4442</v>
+        <v>836</v>
       </c>
       <c r="B393" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
       <c r="C393" t="s">
         <v>764</v>
@@ -60161,7 +60164,7 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="12" t="s">
-        <v>4331</v>
+        <v>4442</v>
       </c>
       <c r="B394" t="s">
         <v>331</v>
@@ -60172,7 +60175,7 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="12" t="s">
-        <v>837</v>
+        <v>4331</v>
       </c>
       <c r="B395" t="s">
         <v>331</v>
@@ -60183,7 +60186,7 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B396" t="s">
         <v>331</v>
@@ -60194,7 +60197,7 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="12" t="s">
-        <v>4441</v>
+        <v>838</v>
       </c>
       <c r="B397" t="s">
         <v>331</v>
@@ -60204,8 +60207,8 @@
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
-        <v>5142</v>
+      <c r="A398" s="12" t="s">
+        <v>4441</v>
       </c>
       <c r="B398" t="s">
         <v>331</v>
@@ -60215,8 +60218,8 @@
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399" s="12" t="s">
-        <v>5143</v>
+      <c r="A399" t="s">
+        <v>5142</v>
       </c>
       <c r="B399" t="s">
         <v>331</v>
@@ -60226,8 +60229,8 @@
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
-        <v>5161</v>
+      <c r="A400" s="12" t="s">
+        <v>5143</v>
       </c>
       <c r="B400" t="s">
         <v>331</v>
@@ -60238,7 +60241,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>5162</v>
+        <v>5161</v>
       </c>
       <c r="B401" t="s">
         <v>331</v>
@@ -60248,19 +60251,19 @@
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A402" s="12" t="s">
-        <v>839</v>
+      <c r="A402" t="s">
+        <v>5162</v>
       </c>
       <c r="B402" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C402" t="s">
-        <v>439</v>
+        <v>764</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B403" t="s">
         <v>335</v>
@@ -60271,7 +60274,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="12" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B404" t="s">
         <v>335</v>
@@ -60282,7 +60285,7 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B405" t="s">
         <v>335</v>
@@ -60293,18 +60296,18 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="12" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B406" t="s">
         <v>335</v>
       </c>
       <c r="C406" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B407" t="s">
         <v>335</v>
@@ -60314,7 +60317,15 @@
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" s="12"/>
+      <c r="A408" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="B408" t="s">
+        <v>335</v>
+      </c>
+      <c r="C408" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="12"/>
@@ -60326,19 +60337,11 @@
       <c r="A411" s="12"/>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" s="12" t="s">
-        <v>845</v>
-      </c>
-      <c r="B412" t="s">
-        <v>335</v>
-      </c>
-      <c r="C412" t="s">
-        <v>764</v>
-      </c>
+      <c r="A412" s="12"/>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B413" t="s">
         <v>335</v>
@@ -60349,7 +60352,7 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B414" t="s">
         <v>335</v>
@@ -60359,39 +60362,39 @@
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" s="12"/>
+      <c r="A415" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="B415" t="s">
+        <v>335</v>
+      </c>
+      <c r="C415" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="12"/>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="B417" t="s">
-        <v>475</v>
-      </c>
-      <c r="C417" t="s">
-        <v>771</v>
-      </c>
+      <c r="A417" s="12"/>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B418" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C418" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="12" t="s">
-        <v>5026</v>
+        <v>849</v>
       </c>
       <c r="B419" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C419" t="s">
         <v>764</v>
@@ -60399,7 +60402,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="12" t="s">
-        <v>5144</v>
+        <v>5026</v>
       </c>
       <c r="B420" t="s">
         <v>331</v>
@@ -60410,7 +60413,7 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="12" t="s">
-        <v>5166</v>
+        <v>5144</v>
       </c>
       <c r="B421" t="s">
         <v>331</v>
@@ -60421,10 +60424,10 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="12" t="s">
-        <v>850</v>
+        <v>5166</v>
       </c>
       <c r="B422" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C422" t="s">
         <v>764</v>
@@ -60432,7 +60435,7 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B423" t="s">
         <v>335</v>
@@ -60443,57 +60446,57 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B424" t="s">
         <v>335</v>
       </c>
       <c r="C424" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="B425" t="s">
+        <v>335</v>
+      </c>
+      <c r="C425" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425" s="12"/>
-    </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="B426" t="s">
-        <v>335</v>
-      </c>
-      <c r="C426" t="s">
-        <v>854</v>
-      </c>
+      <c r="A426" s="12"/>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="12" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B427" t="s">
         <v>335</v>
       </c>
       <c r="C427" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="B428" t="s">
+        <v>335</v>
+      </c>
+      <c r="C428" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428" s="12"/>
-    </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429" s="12" t="s">
-        <v>856</v>
-      </c>
-      <c r="B429" t="s">
-        <v>335</v>
-      </c>
-      <c r="C429" t="s">
-        <v>764</v>
-      </c>
+      <c r="A429" s="12"/>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B430" t="s">
         <v>335</v>
@@ -60504,7 +60507,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="12" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B431" t="s">
         <v>335</v>
@@ -60515,7 +60518,7 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B432" t="s">
         <v>335</v>
@@ -60526,73 +60529,73 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B433" t="s">
         <v>335</v>
       </c>
       <c r="C433" t="s">
-        <v>437</v>
+        <v>764</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B434" t="s">
         <v>335</v>
       </c>
       <c r="C434" t="s">
-        <v>764</v>
+        <v>437</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B435" t="s">
         <v>335</v>
       </c>
       <c r="C435" t="s">
-        <v>329</v>
+        <v>764</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B436" t="s">
         <v>335</v>
       </c>
       <c r="C436" t="s">
-        <v>764</v>
+        <v>329</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B437" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="C437" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B438" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
       <c r="C438" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B439" t="s">
         <v>335</v>
@@ -60603,7 +60606,7 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B440" t="s">
         <v>335</v>
@@ -60614,7 +60617,7 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B441" t="s">
         <v>335</v>
@@ -60625,7 +60628,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B442" t="s">
         <v>335</v>
@@ -60636,7 +60639,7 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B443" t="s">
         <v>335</v>
@@ -60647,7 +60650,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B444" t="s">
         <v>335</v>
@@ -60658,10 +60661,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="12" t="s">
-        <v>5167</v>
+        <v>871</v>
       </c>
       <c r="B445" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C445" t="s">
         <v>764</v>
@@ -60669,7 +60672,7 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="12" t="s">
-        <v>872</v>
+        <v>5167</v>
       </c>
       <c r="B446" t="s">
         <v>331</v>
@@ -60680,7 +60683,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B447" t="s">
         <v>331</v>
@@ -60691,7 +60694,7 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="12" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B448" t="s">
         <v>331</v>
@@ -60701,8 +60704,8 @@
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A449" s="117" t="s">
-        <v>5002</v>
+      <c r="A449" s="12" t="s">
+        <v>874</v>
       </c>
       <c r="B449" t="s">
         <v>331</v>
@@ -60710,11 +60713,10 @@
       <c r="C449" t="s">
         <v>764</v>
       </c>
-      <c r="D449" s="116"/>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A450" s="12" t="s">
-        <v>875</v>
+      <c r="A450" s="117" t="s">
+        <v>5002</v>
       </c>
       <c r="B450" t="s">
         <v>331</v>
@@ -60722,10 +60724,11 @@
       <c r="C450" t="s">
         <v>764</v>
       </c>
+      <c r="D450" s="116"/>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B451" t="s">
         <v>331</v>
@@ -60736,7 +60739,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B452" t="s">
         <v>331</v>
@@ -60747,7 +60750,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B453" t="s">
         <v>331</v>
@@ -60758,7 +60761,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" s="12" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B454" t="s">
         <v>331</v>
@@ -60769,7 +60772,7 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B455" t="s">
         <v>331</v>
@@ -60780,7 +60783,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" s="12" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B456" t="s">
         <v>331</v>
@@ -60791,7 +60794,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B457" t="s">
         <v>331</v>
@@ -60802,7 +60805,7 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" s="12" t="s">
-        <v>4443</v>
+        <v>882</v>
       </c>
       <c r="B458" t="s">
         <v>331</v>
@@ -60813,7 +60816,7 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" s="12" t="s">
-        <v>4473</v>
+        <v>4443</v>
       </c>
       <c r="B459" t="s">
         <v>331</v>
@@ -60824,7 +60827,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" s="12" t="s">
-        <v>4490</v>
+        <v>4473</v>
       </c>
       <c r="B460" t="s">
         <v>331</v>
@@ -60835,7 +60838,7 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" s="12" t="s">
-        <v>5168</v>
+        <v>4490</v>
       </c>
       <c r="B461" t="s">
         <v>331</v>
@@ -60845,8 +60848,8 @@
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
-        <v>5169</v>
+      <c r="A462" s="12" t="s">
+        <v>5168</v>
       </c>
       <c r="B462" t="s">
         <v>331</v>
@@ -60856,8 +60859,8 @@
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A463" s="12" t="s">
-        <v>5170</v>
+      <c r="A463" t="s">
+        <v>5169</v>
       </c>
       <c r="B463" t="s">
         <v>331</v>
@@ -60867,7 +60870,15 @@
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A464" s="12"/>
+      <c r="A464" s="12" t="s">
+        <v>5170</v>
+      </c>
+      <c r="B464" t="s">
+        <v>331</v>
+      </c>
+      <c r="C464" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="12"/>
@@ -60876,33 +60887,25 @@
       <c r="A466" s="12"/>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" s="12" t="s">
+      <c r="A467" s="12"/>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" s="12" t="s">
         <v>883</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B468" t="s">
         <v>475</v>
       </c>
-      <c r="C467" t="s">
+      <c r="C468" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" s="12"/>
-    </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" s="12" t="s">
-        <v>4337</v>
-      </c>
-      <c r="B469" t="s">
-        <v>335</v>
-      </c>
-      <c r="C469" t="s">
-        <v>439</v>
-      </c>
+      <c r="A469" s="12"/>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="12" t="s">
-        <v>4338</v>
+        <v>4337</v>
       </c>
       <c r="B470" t="s">
         <v>335</v>
@@ -60913,7 +60916,7 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="12" t="s">
-        <v>4339</v>
+        <v>4338</v>
       </c>
       <c r="B471" t="s">
         <v>335</v>
@@ -60924,18 +60927,18 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="12" t="s">
-        <v>5093</v>
+        <v>4339</v>
       </c>
       <c r="B472" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C472" t="s">
-        <v>764</v>
+        <v>439</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="12" t="s">
-        <v>4341</v>
+        <v>5093</v>
       </c>
       <c r="B473" t="s">
         <v>331</v>
@@ -60946,18 +60949,18 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="12" t="s">
-        <v>4342</v>
+        <v>4341</v>
       </c>
       <c r="B474" t="s">
         <v>331</v>
       </c>
       <c r="C474" t="s">
-        <v>487</v>
+        <v>764</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="12" t="s">
-        <v>4343</v>
+        <v>4342</v>
       </c>
       <c r="B475" t="s">
         <v>331</v>
@@ -60968,29 +60971,29 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="12" t="s">
-        <v>4344</v>
+        <v>4343</v>
       </c>
       <c r="B476" t="s">
         <v>331</v>
       </c>
       <c r="C476" t="s">
-        <v>764</v>
+        <v>487</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="12" t="s">
-        <v>4345</v>
+        <v>4344</v>
       </c>
       <c r="B477" t="s">
         <v>331</v>
       </c>
       <c r="C477" t="s">
-        <v>487</v>
+        <v>764</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="12" t="s">
-        <v>4346</v>
+        <v>4345</v>
       </c>
       <c r="B478" t="s">
         <v>331</v>
@@ -61001,7 +61004,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="12" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
       <c r="B479" t="s">
         <v>331</v>
@@ -61012,7 +61015,7 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="12" t="s">
-        <v>4348</v>
+        <v>4347</v>
       </c>
       <c r="B480" t="s">
         <v>331</v>
@@ -61023,29 +61026,29 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" s="12" t="s">
-        <v>4349</v>
+        <v>4348</v>
       </c>
       <c r="B481" t="s">
         <v>331</v>
       </c>
       <c r="C481" t="s">
-        <v>764</v>
+        <v>487</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" s="12" t="s">
-        <v>4350</v>
+        <v>4349</v>
       </c>
       <c r="B482" t="s">
         <v>331</v>
       </c>
       <c r="C482" t="s">
-        <v>487</v>
+        <v>764</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" s="12" t="s">
-        <v>4351</v>
+        <v>4350</v>
       </c>
       <c r="B483" t="s">
         <v>331</v>
@@ -61056,7 +61059,7 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" s="12" t="s">
-        <v>4352</v>
+        <v>4351</v>
       </c>
       <c r="B484" t="s">
         <v>331</v>
@@ -61067,7 +61070,7 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" s="12" t="s">
-        <v>4353</v>
+        <v>4352</v>
       </c>
       <c r="B485" t="s">
         <v>331</v>
@@ -61077,24 +61080,32 @@
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" s="13"/>
+      <c r="A486" s="12" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B486" t="s">
+        <v>331</v>
+      </c>
+      <c r="C486" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" s="3" t="s">
+      <c r="A487" s="13"/>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" s="3" t="s">
         <v>4833</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B488" t="s">
         <v>335</v>
       </c>
-      <c r="C487" t="s">
+      <c r="C488" t="s">
         <v>4832</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" s="13"/>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" s="13"/>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" s="13"/>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="13"/>
@@ -63076,8 +63087,11 @@
     <row r="1151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1151" s="13"/>
     </row>
+    <row r="1152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1152" s="13"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1152:A1048576 A3:A8 A64:A115 A171:A177 A198:A208 A211:A214 A43:A61 A10:A17 A179:A196 A216:A229 A19:A41">
+  <conditionalFormatting sqref="A1153:A1048576 A3:A8 A64:A115 A171:A177 A198:A208 A211:A214 A43:A61 A10:A17 A179:A196 A216:A230 A19:A41">
     <cfRule type="duplicateValues" dxfId="32" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A197">
@@ -63099,37 +63113,37 @@
   <conditionalFormatting sqref="A18">
     <cfRule type="duplicateValues" dxfId="25" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A328:A330 A3:A8 A210:A214 A43:A115 A171:A208 A216:A282 A162:A165 E124 A10:A41 A286:A320">
+  <conditionalFormatting sqref="A487:A488 A490 A492:A1048576 D450 A450 A329:A331 A3:A8 A210:A214 A43:A115 A171:A208 A216:A283 A162:A165 E124 A10:A41 A287:A321">
     <cfRule type="duplicateValues" dxfId="24" priority="33"/>
     <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A328:A330 A3:A8 A43:A115 A129:A143 A171:A282 A162:A165 E124 A10:A41 A286:A320">
+  <conditionalFormatting sqref="A487:A488 A490 A492:A1048576 D450 A450 A329:A331 A3:A8 A43:A115 A129:A143 A171:A283 A162:A165 E124 A10:A41 A287:A321">
     <cfRule type="duplicateValues" dxfId="22" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A487 A286 A489 A491:A1048576 D449 A449">
+  <conditionalFormatting sqref="A487:A488 A287 A490 A492:A1048576 D450 A450">
     <cfRule type="duplicateValues" dxfId="21" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A333:A397 A450:A453 A402:A420 A422:A448 A399">
+  <conditionalFormatting sqref="A334:A398 A451:A454 A403:A421 A423:A449 A400">
     <cfRule type="duplicateValues" dxfId="20" priority="97"/>
     <cfRule type="duplicateValues" dxfId="19" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A333:A397 A450:A453 A402:A420 A422:A448 A399">
+  <conditionalFormatting sqref="A334:A398 A451:A454 A403:A421 A423:A449 A400">
     <cfRule type="duplicateValues" dxfId="18" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A454:A461 A463:A485">
+  <conditionalFormatting sqref="A455:A462 A464:A486">
     <cfRule type="duplicateValues" dxfId="17" priority="2"/>
     <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A454:A461 A463:A485">
+  <conditionalFormatting sqref="A455:A462 A464:A486">
     <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A489:A1048576 A1:A331 A333:A397 A402:A461 A463:A487 A399">
+  <conditionalFormatting sqref="A490:A1048576 A1:A332 A334:A398 A403:A462 A464:A488 A400">
     <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A327:A331 A421 A162:A165 E124 A125:A155 A3:A123 A170:A324">
+  <conditionalFormatting sqref="A487:A488 A490 A492:A1048576 D450 A450 A328:A332 A422 A162:A165 E124 A125:A155 A3:A123 A170:A325">
     <cfRule type="duplicateValues" dxfId="13" priority="160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A487 A489 A491:A1048576 D449 A449 A327:A331 A421 A3:A324">
+  <conditionalFormatting sqref="A487:A488 A490 A492:A1048576 D450 A450 A328:A332 A422 A3:A325">
     <cfRule type="duplicateValues" dxfId="12" priority="178"/>
     <cfRule type="duplicateValues" dxfId="11" priority="179"/>
   </conditionalFormatting>
